--- a/花开富贵.xlsx
+++ b/花开富贵.xlsx
@@ -1,22 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView windowWidth="18060" windowHeight="15500"/>
   </bookViews>
   <sheets>
-    <sheet name="工作表1" sheetId="1" r:id="rId3"/>
+    <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
-  <si>
-    <t/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>花开富贵鲜花集锦💐</t>
   </si>
@@ -24,7 +35,7 @@
     <t>魔力卡花匠</t>
   </si>
   <si>
-    <t>蓝铁21，幻紫23、紫麦冬花14、雾粉麦冬花21、粉白君子兰14、嫣红杜鹃花14</t>
+    <t>蓝铁，幻紫、紫麦冬花、雾粉麦冬花、粉白君子兰、嫣红杜鹃花</t>
   </si>
   <si>
     <t>董沅芹</t>
@@ -36,7 +47,7 @@
     <t>耶律姝艳</t>
   </si>
   <si>
-    <t>粉满天星14，玫红非洲堇14，鸳鸯茉莉，绿铁，浅黄绿绒蒿，幽兰绿绒蒿，正红大丽花，薄粉蕙兰，淡茜蜀葵花，三色络新妇，杏黄杜鹃，紫粉矢车菊，香槟玫瑰，明黄跳舞兰，绯色腊梅，梦紫郁金香</t>
+    <t>粉色满天星14，玫红非洲堇14，鸳鸯茉莉，绿铁，浅黄绿绒蒿，幽兰绿绒蒿，正红大丽花，薄粉蕙兰，淡茜蜀葵花，三色络新妇，杏黄杜鹃，紫粉矢车菊，香槟玫瑰，明黄跳舞兰，绯色腊梅，梦紫郁金香</t>
   </si>
   <si>
     <t>长孙若微</t>
@@ -95,44 +106,184 @@
   </si>
   <si>
     <t>粉紫华珊、香槟玫瑰、鸳鸯茉莉，木槿花、冬青、紫郁金香、冰蓝矮牵牛、淡茜蜀葵花、月白格桑花</t>
-  </si>
-  <si>
-    <t>粉色满天星14，玫红非洲堇14，鸳鸯茉莉，绿铁，浅黄绿绒蒿，幽兰绿绒蒿，正红大丽花，薄粉蕙兰，淡茜蜀葵花，三色络新妇，杏黄杜鹃，紫粉矢车菊，香槟玫瑰，明黄跳舞兰，绯色腊梅，梦紫郁金香</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="6">
-    <font>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
+    <font>
+      <sz val="10"/>
       <name val="Microsoft YaHei"/>
-    </font>
-    <font>
-      <name val="等线"/>
       <charset val="134"/>
-      <color rgb="FF175CEB"/>
-      <sz val="10"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Segoe UI Symbol"/>
-      <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="18"/>
-    </font>
-    <font/>
-    <font>
-      <name val="Microsoft YaHei"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -140,10 +291,193 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -151,43 +485,544 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs>
-    <xf fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="2" borderId="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="2" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles>
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="">
       <a:dk1>
@@ -417,125 +1252,124 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor/>
-  </sheetPr>
-  <dimension ref="B14"/>
-  <sheetFormatPr baseColWidth="13" defaultRowHeight="18" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D27"/>
+  <sheetFormatPr defaultColWidth="14" defaultRowHeight="18" customHeight="1" outlineLevelCol="3"/>
   <cols>
-    <col min="4" max="4" width="34.8008" customWidth="1"/>
+    <col min="4" max="4" width="34.8046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="58.5" customHeight="1">
-      <c r="A1" s="4" t="s">
+    <row r="1" ht="58.5" customHeight="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" ht="42.75" customHeight="1" spans="1:2">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" ht="42.75" customHeight="1">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="5" t="s">
+    <row r="3" ht="42.75" customHeight="1" spans="1:2">
+      <c r="A3" t="s">
         <v>3</v>
       </c>
+      <c r="B3" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="3" spans="1:2" ht="42.75" customHeight="1">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="5" t="s">
+    <row r="4" ht="42" customHeight="1" spans="1:2">
+      <c r="A4" t="s">
         <v>5</v>
       </c>
+      <c r="B4" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="4" spans="1:2" ht="42" customHeight="1">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>27</v>
+    <row r="5" ht="48" customHeight="1" spans="1:2">
+      <c r="A5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="48" customHeight="1">
-      <c r="A5" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="5" t="s">
+    <row r="6" ht="51" customHeight="1" spans="1:2">
+      <c r="A6" t="s">
         <v>9</v>
       </c>
+      <c r="B6" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="6" spans="1:2" ht="51" customHeight="1">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="5" t="s">
+    <row r="7" ht="62.25" customHeight="1" spans="1:2">
+      <c r="A7" t="s">
         <v>11</v>
       </c>
+      <c r="B7" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="7" spans="1:2" ht="62.25" customHeight="1">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="5" t="s">
+    <row r="8" ht="49.5" customHeight="1" spans="1:2">
+      <c r="A8" t="s">
         <v>13</v>
       </c>
+      <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="8" spans="1:2" ht="49.5" customHeight="1">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="5" t="s">
+    <row r="9" ht="51" customHeight="1" spans="1:2">
+      <c r="A9" t="s">
         <v>15</v>
       </c>
+      <c r="B9" s="2"/>
     </row>
-    <row r="9" spans="1:2" ht="51" customHeight="1">
-      <c r="A9" t="s">
+    <row r="10" ht="60" customHeight="1" spans="1:2">
+      <c r="A10" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="5" t="s"/>
+      <c r="B10" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="10" spans="1:2" ht="60" customHeight="1">
-      <c r="A10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="5" t="s">
+    <row r="11" ht="50.25" customHeight="1" spans="1:2">
+      <c r="A11" t="s">
         <v>18</v>
       </c>
+      <c r="B11" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="11" spans="1:2" ht="50.25" customHeight="1">
-      <c r="A11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="5" t="s">
+    <row r="12" ht="54.75" customHeight="1" spans="1:2">
+      <c r="A12" t="s">
         <v>20</v>
       </c>
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="12" spans="1:2" ht="54.75" customHeight="1">
-      <c r="A12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" t="s">
+    <row r="13" ht="15.2" spans="1:2">
+      <c r="A13" t="s">
         <v>22</v>
       </c>
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" t="s">
+    <row r="14" ht="60" customHeight="1" spans="1:2">
+      <c r="A14" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" ht="60" customHeight="1">
-      <c r="A14" t="s">
+      <c r="B14" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -568,5 +1402,7 @@
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="B27:D27"/>
   </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/花开富贵.xlsx
+++ b/花开富贵.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18060" windowHeight="15500"/>
+    <workbookView windowWidth="23420" windowHeight="15500"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -35,43 +35,43 @@
     <t>魔力卡花匠</t>
   </si>
   <si>
-    <t>蓝铁，幻紫、紫麦冬花、雾粉麦冬花、粉白君子兰、嫣红杜鹃花</t>
+    <t>蓝叶苏铁，幻紫铁线莲、紫麦冬花、雾粉麦冬花、粉白君子兰、嫣红杜鹃</t>
   </si>
   <si>
     <t>董沅芹</t>
   </si>
   <si>
-    <t>蓝铁、赤焰、珠宝之心</t>
+    <t>蓝叶苏铁、赤焰火焰兰、珠宝之心</t>
   </si>
   <si>
     <t>耶律姝艳</t>
   </si>
   <si>
-    <t>粉色满天星14，玫红非洲堇14，鸳鸯茉莉，绿铁，浅黄绿绒蒿，幽兰绿绒蒿，正红大丽花，薄粉蕙兰，淡茜蜀葵花，三色络新妇，杏黄杜鹃，紫粉矢车菊，香槟玫瑰，明黄跳舞兰，绯色腊梅，梦紫郁金香</t>
+    <t>粉色满天星，玫红非洲堇，鸳鸯茉莉，绿叶苏铁，浅黄绿绒蒿，幽兰绿绒蒿，正红大丽花，薄粉蕙兰，淡茜蜀葵花，杏黄杜鹃、紫矢车菊、粉矢车菊、香槟玫瑰，明黄跳舞兰，绯色腊梅，梦紫郁金香</t>
   </si>
   <si>
     <t>长孙若微</t>
   </si>
   <si>
-    <t>殷红灯笼花，白花马齿笕，嫩黄马齿笕，蓝色满天星，粉蓝紫矢车菊，浅蓝紫红落新妇，绿铁，蓝色牵牛花浅粉夹竹桃</t>
+    <t>殷红灯笼花，白花马齿笕，嫩黄马齿笕，蓝色满天星，紫矢车菊、粉矢车菊、蓝矢车菊，绿叶苏铁，蓝色牵牛花，浅粉夹竹桃</t>
   </si>
   <si>
     <t>大稻</t>
   </si>
   <si>
-    <t>蓝面花、钢丝球、鹅黄铁筷花，朱柿长寿花，绯色腊梅、</t>
+    <t>澄蓝龙面花、葡萄紫牡丹球、鹅黄铁筷花，朱柿长寿花，绯色腊梅、伯利恒之星、碧落月见草、绛粉大岩桐</t>
   </si>
   <si>
     <t>慕蕊</t>
   </si>
   <si>
-    <t>浅韵美女樱、粉鹤、紫美人、紫葱、伯利恒之星、红/白垂筒花、柔紫石斛兰、紫荷包牡丹、三色车菊、忽地笑、杏白忘忧草、淡粉马齿苋、银白翠竹、正红大丽花、月白格桑花、三色落新妇、淡茜蜀葵花、曼陀罗化、星河、金蝉腰、粉樱月见草、碧落月见草、绯色腊梅、藤黄露薇花、莹白露薇花、粉/白谷鸢尾花</t>
+    <t>浅韵美女樱、粉鹤芋、黛紫紫美人、轻紫大花葱、伯利恒之星、橘红垂筒花、霜白垂筒花、柔紫石斛兰、紫荷包牡丹、紫矢车菊、粉矢车菊、蓝矢车菊、忽地笑、杏白忘忧草、淡粉马齿苋、银白翠珠、正红大丽花、月白格桑花、淡茜蜀葵花、曼陀罗花、星河映蕊、金缠腰、粉樱月见草、碧落月见草、绯色腊梅、藤黄露薇花、莹白露薇花、霜白谷鸢尾花、冰蓝谷鸢尾</t>
   </si>
   <si>
     <t>暖香</t>
   </si>
   <si>
-    <t>曼莎珠华，鸳鸯茉莉、橙黄美人、粉鹤、伯利恒，绿铁，三色矢车菊，三色落新妇，三色垂筒花，浅橘/明黄如意菊，柔紫/碧白石斛兰，粉/白谷鸢尾，蓝/黄/粉牵牛，轻紫翠竹、丹紫夹竹桃</t>
+    <t>曼珠沙华，鸳鸯茉莉、橙黄虞美人、粉鹤芋、伯利恒之星，绿叶苏铁，紫矢车菊、粉矢车菊、蓝矢车菊、霜白垂筒花、橘红垂筒花、明黄垂筒花、浅橘如意菊、明黄如意菊，柔紫石斛兰、碧白石斛兰，桃粉谷鸢尾、霜白谷鸢尾，冰蓝矮牵牛、明黄矮牵牛、淡粉矮牵牛，轻紫翠珠、丹紫夹竹桃</t>
   </si>
   <si>
     <t>绿豆</t>
@@ -80,13 +80,13 @@
     <t>千婷</t>
   </si>
   <si>
-    <t>绿铁、蓝色满天星</t>
+    <t>绿叶苏铁、蓝色满天星</t>
   </si>
   <si>
     <t>丧彪</t>
   </si>
   <si>
-    <t xml:space="preserve">黑曜大丽花 浅紫落新妇  浅蓝络新妇  蓝色牵牛花 
+    <t xml:space="preserve">黑曜大丽花 冰蓝矮牵牛
 </t>
   </si>
   <si>
@@ -99,13 +99,13 @@
     <t>嘉文</t>
   </si>
   <si>
-    <t>轻紫翠竹、金盏蜀葵花</t>
+    <t>轻紫翠珠、金盏蜀葵花</t>
   </si>
   <si>
     <t>上官雁</t>
   </si>
   <si>
-    <t>粉紫华珊、香槟玫瑰、鸳鸯茉莉，木槿花、冬青、紫郁金香、冰蓝矮牵牛、淡茜蜀葵花、月白格桑花</t>
+    <t>粉紫华珊、香槟玫瑰、鸳鸯茉莉，粉红木槿花、轮生冬青、梦紫郁金香、冰蓝矮牵牛、淡茜蜀葵花、月白格桑花</t>
   </si>
 </sst>
 </file>
@@ -1286,7 +1286,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" ht="42" customHeight="1" spans="1:2">
+    <row r="4" ht="116" customHeight="1" spans="1:2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1294,7 +1294,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" ht="48" customHeight="1" spans="1:2">
+    <row r="5" ht="125" customHeight="1" spans="1:2">
       <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
@@ -1302,7 +1302,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" ht="51" customHeight="1" spans="1:2">
+    <row r="6" ht="129" customHeight="1" spans="1:2">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1310,7 +1310,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" ht="62.25" customHeight="1" spans="1:2">
+    <row r="7" ht="232" customHeight="1" spans="1:2">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1318,7 +1318,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" ht="49.5" customHeight="1" spans="1:2">
+    <row r="8" ht="123" customHeight="1" spans="1:2">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -1356,7 +1356,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" ht="15.2" spans="1:2">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>22</v>
       </c>
